--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -36,27 +36,27 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Elena</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocopilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calama</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,13 +493,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2203</v>
+        <v>2102</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>474</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3">
@@ -510,13 +510,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2103</v>
+        <v>2301</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +550,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-63</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="7">
@@ -578,13 +578,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2104</v>
+        <v>2203</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-307</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="8">
@@ -595,13 +595,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2301</v>
+        <v>2103</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1380</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="9">
@@ -609,16 +609,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-9310</v>
+        <v>-2305</v>
       </c>
     </row>
     <row r="10">
@@ -626,16 +626,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-10073</v>
+        <v>-2893</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:52</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-05 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
